--- a/cfg/excel/CharacterCfg.xlsx
+++ b/cfg/excel/CharacterCfg.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\Shooting\Luban\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Shooting\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25530" windowHeight="13545"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -174,28 +174,10 @@
     <t>EnemyAI</t>
   </si>
   <si>
-    <t>Collection1</t>
-  </si>
-  <si>
-    <t>弹药收集物</t>
-  </si>
-  <si>
-    <t>Collection2</t>
-  </si>
-  <si>
-    <t>护甲收集物</t>
-  </si>
-  <si>
-    <t>Collection3</t>
-  </si>
-  <si>
-    <t>血包收集物</t>
-  </si>
-  <si>
-    <t>Collection4</t>
-  </si>
-  <si>
-    <t>防弹衣收集物</t>
+    <t>Collection</t>
+  </si>
+  <si>
+    <t>收集物</t>
   </si>
   <si>
     <t>Sniper</t>
@@ -1418,11 +1400,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="2" width="10.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18.7" style="3" customWidth="1"/>
+    <col min="3" max="3" width="24.75" style="3" customWidth="1"/>
     <col min="4" max="4" width="18.0666666666667" style="3" customWidth="1"/>
     <col min="5" max="5" width="27.6666666666667" style="3" customWidth="1"/>
     <col min="6" max="6" width="15.25" style="3" customWidth="1"/>
@@ -1727,9 +1709,9 @@
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" ht="20.25" spans="1:15">
       <c r="B9" s="3">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>48</v>
@@ -1737,130 +1719,91 @@
       <c r="D9" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3">
+        <v>5</v>
+      </c>
+      <c r="K9" s="3">
+        <v>50</v>
+      </c>
+      <c r="L9" s="3">
+        <v>720</v>
+      </c>
+      <c r="M9" s="3">
+        <v>100</v>
+      </c>
       <c r="N9" s="3">
         <v>1</v>
       </c>
-      <c r="O9" s="4"/>
+      <c r="O9" s="5" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" ht="20.25" spans="1:15">
       <c r="B10" s="3">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2</v>
+      </c>
+      <c r="G10" s="3">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3">
         <v>50</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>51</v>
+      <c r="L10" s="3">
+        <v>720</v>
+      </c>
+      <c r="M10" s="3">
+        <v>100</v>
       </c>
       <c r="N10" s="3">
         <v>1</v>
       </c>
-      <c r="O10" s="4"/>
+      <c r="O10" s="5" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="11" spans="1:15">
       <c r="B11" s="3">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N11" s="3">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="O11" s="4"/>
     </row>
-    <row r="12" ht="20.25" spans="1:15">
-      <c r="B12" s="3">
-        <v>1010</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="3">
-        <v>2</v>
-      </c>
-      <c r="G12" s="3">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3">
-        <v>5</v>
-      </c>
-      <c r="K12" s="3">
-        <v>50</v>
-      </c>
-      <c r="L12" s="3">
-        <v>720</v>
-      </c>
-      <c r="M12" s="3">
-        <v>100</v>
-      </c>
-      <c r="N12" s="3">
-        <v>1</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>56</v>
-      </c>
+    <row r="12" spans="1:15">
+      <c r="O12" s="4"/>
     </row>
-    <row r="13" ht="20.25" spans="1:15">
-      <c r="B13" s="3">
-        <v>1011</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="3">
-        <v>2</v>
-      </c>
-      <c r="G13" s="3">
-        <v>3</v>
-      </c>
-      <c r="I13" s="3">
-        <v>3</v>
-      </c>
-      <c r="J13" s="3">
-        <v>5</v>
-      </c>
-      <c r="K13" s="3">
-        <v>50</v>
-      </c>
-      <c r="L13" s="3">
-        <v>720</v>
-      </c>
-      <c r="M13" s="3">
-        <v>100</v>
-      </c>
-      <c r="N13" s="3">
-        <v>1</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>59</v>
-      </c>
+    <row r="13" spans="1:15">
+      <c r="O13" s="4"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="B14" s="3">
-        <v>1012</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0.1</v>
-      </c>
       <c r="O14" s="4"/>
     </row>
     <row r="15" spans="1:15">
@@ -1877,15 +1820,6 @@
     </row>
     <row r="19" spans="15:15">
       <c r="O19" s="4"/>
-    </row>
-    <row r="20" spans="15:15">
-      <c r="O20" s="4"/>
-    </row>
-    <row r="21" spans="15:15">
-      <c r="O21" s="4"/>
-    </row>
-    <row r="22" spans="15:15">
-      <c r="O22" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
